--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104524_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104524_W8.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9095</v>
+        <v>5.028</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6213</v>
+        <v>1.6092</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2882</v>
+        <v>3.4188</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7324</v>
+        <v>4.732</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5467</v>
+        <v>2.5529</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1857</v>
+        <v>2.179</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1482</v>
+        <v>3.1219</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8875</v>
+        <v>1.8788</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2607</v>
+        <v>1.243</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5842</v>
+        <v>1.6101</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O2" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2519</v>
+        <v>-0.1381</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3266</v>
+        <v>-0.3046</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0747</v>
+        <v>0.1666</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2238</v>
+        <v>4.6523</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5169</v>
+        <v>2.6666</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7069</v>
+        <v>1.9856</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3268</v>
+        <v>2.3365</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6204</v>
+        <v>1.6226</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7064</v>
+        <v>0.7139</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8617</v>
+        <v>2.8504</v>
       </c>
       <c r="K3" t="n">
-        <v>2.078</v>
+        <v>2.0684</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5139</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0823</v>
+        <v>0.4947</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1179</v>
+        <v>0.0439</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2002</v>
+        <v>0.4509</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8063</v>
+        <v>4.2696</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9867</v>
+        <v>2.4196</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8196</v>
+        <v>1.85</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0611</v>
+        <v>5.0594</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5684</v>
+        <v>3.5699</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4927</v>
+        <v>1.4895</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9755</v>
+        <v>3.9507</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5629</v>
+        <v>2.5511</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0856</v>
+        <v>1.1087</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0055</v>
+        <v>1.0189</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7349</v>
+        <v>-0.2647</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9739</v>
+        <v>-0.5021</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2389</v>
+        <v>0.2374</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3174</v>
+        <v>3.0417</v>
       </c>
       <c r="E5" t="n">
-        <v>2.174</v>
+        <v>1.6818</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1434</v>
+        <v>1.3599</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2814</v>
+        <v>2.2689</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8069</v>
+        <v>1.7875</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4745</v>
+        <v>0.4815</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3198</v>
+        <v>3.2856</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6108</v>
+        <v>2.5781</v>
       </c>
       <c r="L5" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0384</v>
+        <v>-1.0166</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2855</v>
+        <v>0.0232</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5989</v>
+        <v>0.1506</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3133</v>
+        <v>-0.1275</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0572</v>
+        <v>2.7608</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5024</v>
+        <v>0.2278</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5548</v>
+        <v>2.533</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8711</v>
+        <v>2.195</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2204</v>
+        <v>2.1032</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9351</v>
+        <v>0.8458</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0693</v>
+        <v>-0.1519</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8658</v>
+        <v>0.9977</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.3492</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5814</v>
+        <v>0.2437</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3546</v>
+        <v>1.1055</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4025</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7493</v>
+        <v>0.3578</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8771</v>
+        <v>-0.3904</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8722</v>
+        <v>0.7482</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.7025</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5721</v>
+        <v>2.1788</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.2714</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6353</v>
+        <v>2.4501</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1952</v>
+        <v>2.8799</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.6573</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1057</v>
+        <v>2.2226</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8592</v>
+        <v>1.9308</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1456</v>
+        <v>0.0689</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0048</v>
+        <v>1.8618</v>
       </c>
       <c r="M7" t="n">
-        <v>1.336</v>
+        <v>0.9492</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2351</v>
+        <v>0.5884</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1009</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1766</v>
+        <v>0.871</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6956</v>
+        <v>0.1228</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8722</v>
+        <v>0.7482</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7071</v>
+        <v>0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7071</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.528</v>
+        <v>0.802</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4228</v>
+        <v>-0.0233</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9508</v>
+        <v>0.8253</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8172</v>
+        <v>2.8219</v>
       </c>
       <c r="H8" t="n">
-        <v>0.834</v>
+        <v>0.833</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9832</v>
+        <v>1.9889</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5426</v>
+        <v>1.5264</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3605</v>
+        <v>-0.3727</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2746</v>
+        <v>1.2955</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1946</v>
+        <v>1.2057</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.189</v>
+        <v>0.4566</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>-0.3417</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9542</v>
+        <v>0.7983</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.42</v>
+        <v>0.7916</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2817</v>
+        <v>0.3686</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7016</v>
+        <v>0.423</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2789</v>
+        <v>2.2861</v>
       </c>
       <c r="H9" t="n">
-        <v>1.29</v>
+        <v>1.2923</v>
       </c>
       <c r="I9" t="n">
-        <v>0.989</v>
+        <v>0.9938</v>
       </c>
       <c r="J9" t="n">
-        <v>1.886</v>
+        <v>1.8669</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2917</v>
+        <v>1.2788</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3929</v>
+        <v>0.4192</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0484</v>
+        <v>0.416</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7652</v>
+        <v>-0.0838</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8135</v>
+        <v>0.4999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1904</v>
+        <v>-1.0159</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8381</v>
+        <v>-0.132</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0285</v>
+        <v>-0.8839</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1507</v>
+        <v>0.1535</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9192</v>
+        <v>4.7052</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2315</v>
+        <v>-4.5517</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6729</v>
+        <v>1.5846</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1083</v>
+        <v>4.6917</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5646</v>
+        <v>-3.1071</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5222</v>
+        <v>-1.431</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1891</v>
+        <v>0.0135</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3331</v>
+        <v>-1.4446</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0611</v>
+        <v>0.1963</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2994</v>
+        <v>-0.4811</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3605</v>
+        <v>0.6774</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.0531</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0531</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5093</v>
+        <v>-1.2379</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6191</v>
+        <v>1.7046</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8902</v>
+        <v>-2.9425</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1871</v>
+        <v>2.1452</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7187</v>
+        <v>0.9164</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.5316</v>
+        <v>1.2288</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6414</v>
+        <v>2.6594</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7204</v>
+        <v>1.1032</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.0789</v>
+        <v>1.5563</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4543</v>
+        <v>-0.5143</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0017</v>
+        <v>-0.1868</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4526</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3354</v>
+        <v>-0.1163</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0434</v>
+        <v>0.1833</v>
       </c>
       <c r="U11" t="n">
-        <v>0.708</v>
+        <v>-0.2995</v>
       </c>
       <c r="V11" t="n">
+        <v>-3.0392</v>
+      </c>
+      <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.1853</v>
-      </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-3.0392</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8053</v>
+        <v>-2.5628</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2121</v>
+        <v>-3.1612</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4067</v>
+        <v>0.5984</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6122</v>
+        <v>-0.6132</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2887</v>
+        <v>0.2818</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9009</v>
+        <v>-0.895</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3065</v>
+        <v>-0.3309</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2291</v>
+        <v>-0.2488</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3057</v>
+        <v>-0.2822</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1043</v>
+        <v>0.1429</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1875</v>
+        <v>-0.0955</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0832</v>
+        <v>0.2385</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0888</v>
+        <v>-2.0926</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.3293</v>
+        <v>18.7082</v>
       </c>
       <c r="E13" t="n">
-        <v>6.040500000000002</v>
+        <v>7.0903</v>
       </c>
       <c r="F13" t="n">
-        <v>11.2886</v>
+        <v>11.6177</v>
       </c>
       <c r="G13" t="n">
-        <v>26.2897</v>
+        <v>26.2652</v>
       </c>
       <c r="H13" t="n">
-        <v>18.3331</v>
+        <v>18.3107</v>
       </c>
       <c r="I13" t="n">
-        <v>7.956600000000002</v>
+        <v>7.954499999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>23.5359</v>
+        <v>23.29160000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>15.5937</v>
+        <v>15.4456</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9426</v>
+        <v>7.846</v>
       </c>
       <c r="M13" t="n">
-        <v>2.753900000000001</v>
+        <v>2.9739</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7396</v>
+        <v>2.865200000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01410000000000033</v>
+        <v>0.1085000000000002</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1466</v>
+        <v>18.2105</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0435</v>
+        <v>2.4394</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.0999</v>
+        <v>-1.6986</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1433</v>
+        <v>4.138400000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.869700000000002</v>
+        <v>-8.858599999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>4.8852</v>
+        <v>4.8461</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.7549</v>
+        <v>-13.7047</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6377</v>
+        <v>2.2883</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4705</v>
+        <v>2.1822</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1672</v>
+        <v>0.1061</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.7318</v>
+        <v>-3.7311</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.1658</v>
+        <v>-5.1641</v>
       </c>
       <c r="I14" t="n">
-        <v>1.434</v>
+        <v>1.433</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8252</v>
+        <v>-0.8486</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.0242</v>
+        <v>-3.0379</v>
       </c>
       <c r="L14" t="n">
-        <v>2.199</v>
+        <v>2.1893</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.9065</v>
+        <v>-2.8825</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.1416</v>
+        <v>-2.1262</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5846</v>
+        <v>0.2565</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2208</v>
+        <v>-0.4558</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8054</v>
+        <v>0.7123</v>
       </c>
       <c r="V14" t="n">
-        <v>5.7848</v>
+        <v>5.7629</v>
       </c>
       <c r="W14" t="n">
-        <v>5.7848</v>
+        <v>5.7629</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.89</v>
+        <v>1.7779</v>
       </c>
       <c r="E15" t="n">
-        <v>0.446</v>
+        <v>0.4357</v>
       </c>
       <c r="F15" t="n">
-        <v>1.444</v>
+        <v>1.3421</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6673</v>
+        <v>-0.659</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0592</v>
+        <v>-1.057</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3919</v>
+        <v>0.398</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1083</v>
+        <v>-0.1146</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5444</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1893</v>
+        <v>-0.3159</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5383</v>
+        <v>-0.5391</v>
       </c>
       <c r="U15" t="n">
-        <v>0.349</v>
+        <v>0.2232</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.262</v>
+        <v>0.7327</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5477</v>
+        <v>2.7679</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2857</v>
+        <v>-2.0352</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0677</v>
+        <v>-0.0626</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5556</v>
+        <v>-0.5544</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4878</v>
+        <v>0.4917</v>
       </c>
       <c r="J16" t="n">
-        <v>3.207</v>
+        <v>3.191</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8934</v>
+        <v>0.8823</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3136</v>
+        <v>2.3087</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2747</v>
+        <v>-3.2536</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4489</v>
+        <v>-1.4367</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P16" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2996</v>
+        <v>-0.8468</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6593</v>
+        <v>-0.4231</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6403</v>
+        <v>-0.4237</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1894</v>
+        <v>0.4998</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3979</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5873</v>
+        <v>0.4216</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6413</v>
+        <v>0.9478</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4574</v>
+        <v>-0.7561</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1839</v>
+        <v>1.7039</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8347</v>
+        <v>1.7789</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9839</v>
+        <v>0.3792</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>1.3997</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8066</v>
+        <v>-0.831</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4735</v>
+        <v>-1.1353</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3331</v>
+        <v>0.3043</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8042</v>
+        <v>-0.4983</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3176</v>
+        <v>-0.5625</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4866</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2534</v>
+        <v>-0.8603</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.027</v>
+        <v>-0.0885</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.139</v>
+        <v>-0.415</v>
       </c>
       <c r="F18" t="n">
-        <v>0.166</v>
+        <v>0.3264</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9393</v>
+        <v>-1.632</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7693</v>
+        <v>-1.4535</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7086</v>
+        <v>-0.1785</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7936</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.381</v>
+        <v>-0.9932</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4126</v>
+        <v>0.1489</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.7877</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1503</v>
+        <v>-0.4603</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2959</v>
+        <v>-0.3275</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9518</v>
+        <v>0.5239</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7984</v>
+        <v>0.3202</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1534</v>
+        <v>0.2036</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8678</v>
+        <v>1.2472</v>
       </c>
       <c r="W18" t="n">
+        <v>1.2472</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.8678</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0044</v>
+        <v>-0.573</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.5779</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0827</v>
+        <v>0.0049</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.89</v>
+        <v>-1.8923</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0159</v>
+        <v>0.0144</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9059</v>
+        <v>-1.9067</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9737</v>
+        <v>-0.99</v>
       </c>
       <c r="K19" t="n">
-        <v>0.599</v>
+        <v>0.5893</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9162</v>
+        <v>-0.9023</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5483</v>
+        <v>-0.0174</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2299</v>
+        <v>-0.2418</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3185</v>
+        <v>0.2243</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6223</v>
+        <v>-1.8925</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9402</v>
+        <v>0.4568</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5624</v>
+        <v>-2.3492</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2238</v>
+        <v>-2.2119</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8832</v>
+        <v>-0.8791</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3407</v>
+        <v>-1.3329</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9605</v>
+        <v>0.9563</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L20" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1843</v>
+        <v>-3.1683</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7317</v>
+        <v>-1.7237</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>0.216</v>
+        <v>-0.0675</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0212</v>
+        <v>-0.4509</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1948</v>
+        <v>0.3834</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1216</v>
+        <v>-2.2359</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7785</v>
+        <v>-1.4631</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3431</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1465</v>
+        <v>-2.1515</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.547</v>
+        <v>-0.5376</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5994</v>
+        <v>-1.6139</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6028</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4373</v>
+        <v>1.4307</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8345</v>
+        <v>-0.8576</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7493</v>
+        <v>-2.7246</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9843</v>
+        <v>-1.9683</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3463</v>
+        <v>0.2312</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6593</v>
+        <v>-0.3046</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0056</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.656</v>
+        <v>-2.3933</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8185</v>
+        <v>-2.5995</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1625</v>
+        <v>0.2062</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2001</v>
+        <v>-3.2074</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9233</v>
+        <v>-1.9324</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2768</v>
+        <v>-1.275</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3315</v>
+        <v>-2.3484</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5452</v>
+        <v>-1.5588</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8685</v>
+        <v>-0.859</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3632</v>
+        <v>-0.0964</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1237</v>
+        <v>0.1546</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4437</v>
+        <v>-2.9585</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8554</v>
+        <v>-3.4371</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4117</v>
+        <v>0.4786</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7724</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7804</v>
+        <v>-0.7948</v>
       </c>
       <c r="I23" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6601</v>
+        <v>0.6189</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8894</v>
+        <v>0.8576</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4325</v>
+        <v>-1.4047</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6698</v>
+        <v>-1.6524</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2423</v>
+        <v>0.2614</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.113</v>
+        <v>-0.6415</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8707</v>
+        <v>0.9028</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6233</v>
+        <v>-5.6783</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5307</v>
+        <v>-4.8068</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0926</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7463</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6249</v>
+        <v>-1.6147</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.1214</v>
+        <v>-3.1316</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.7884</v>
+        <v>-2.8126</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.1406</v>
+        <v>-2.1608</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9579</v>
+        <v>-1.9337</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3799</v>
+        <v>-0.4297</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4011</v>
+        <v>-0.2157</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W24" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8728</v>
+        <v>-6.7925</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0947</v>
+        <v>-4.2392</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7781</v>
+        <v>-2.5533</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.1417</v>
+        <v>-6.1329</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.5829</v>
+        <v>-3.5816</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.5588</v>
+        <v>-2.5514</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1157</v>
+        <v>-2.1333</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.4413</v>
+        <v>-1.4554</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.026</v>
+        <v>-3.9996</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.1416</v>
+        <v>-2.1262</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1167</v>
+        <v>-0.0466</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2571</v>
+        <v>-0.3743</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1403</v>
+        <v>0.3278</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.3292</v>
+        <v>-17.3138</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.2886</v>
+        <v>-11.6178</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.0405</v>
+        <v>-5.696</v>
       </c>
       <c r="G26" t="n">
-        <v>-26.2896</v>
+        <v>-26.265</v>
       </c>
       <c r="H26" t="n">
-        <v>-18.3331</v>
+        <v>-18.3109</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.9566</v>
+        <v>-7.954400000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.7535</v>
+        <v>-2.9736</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.7394</v>
+        <v>-2.8652</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.01409999999999967</v>
+        <v>-0.1085</v>
       </c>
       <c r="M26" t="n">
-        <v>-23.5358</v>
+        <v>-23.2914</v>
       </c>
       <c r="N26" t="n">
-        <v>-15.5935</v>
+        <v>-15.4457</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.942200000000001</v>
+        <v>-7.8459</v>
       </c>
       <c r="P26" t="n">
-        <v>1.1341</v>
+        <v>1.138099999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-18.1467</v>
+        <v>-18.2107</v>
       </c>
       <c r="R26" t="n">
-        <v>19.2808</v>
+        <v>19.3488</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0434</v>
+        <v>-1.0456</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.1432</v>
+        <v>-4.138400000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>3.0998</v>
+        <v>3.0926</v>
       </c>
       <c r="V26" t="n">
-        <v>8.8698</v>
+        <v>8.858600000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>13.7549</v>
+        <v>13.7047</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.885299999999999</v>
+        <v>-4.8462</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104524_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104524_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.0392</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-13.7047</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104524_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-4.8462</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
